--- a/benchmark/notebooks/comparison_tables.xlsx
+++ b/benchmark/notebooks/comparison_tables.xlsx
@@ -461,14 +461,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,10 +493,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>golinski</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>otl_circuit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>piston</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>rastrigin_6d</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -514,12 +538,32 @@
           <t>0.529 ± 0.88</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>0.0769 ± 0.094</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.00142 ± 0.0028</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.00104 ± 0.00071</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>18.2 ± 9.6</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.2 ± 0.33</t>
         </is>
@@ -541,12 +585,32 @@
           <t>0.238 ± 0.59</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>0.0349 ± 0.062</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>6.94e-05 ± 7e-05</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>0.000532 ± 0.00038</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>13.6 ± 3.8</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>0.0684 ± 0.19</t>
         </is>
@@ -568,12 +632,32 @@
           <t>0.662 ± 0.95</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>0.029 ± 0.049</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>3.07e-05 ± 6.1e-05</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.001 ± 0.00074</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>12.2 ± 8</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>0.0457 ± 0.18</t>
         </is>
@@ -597,10 +681,30 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>0.0288 ± 0.049</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>3.07e-05 ± 6.1e-05</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.000822 ± 0.00057</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>9.46 ± 2.4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.0486 ± 0.15</t>
         </is>
@@ -622,12 +726,32 @@
           <t>0.666 ± 1.1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>0.0413 ± 0.048</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.000162 ± 0.00029</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.00209 ± 0.0007</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12.6 ± 3.4</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>0.000237 ± 0.00041</t>
         </is>
@@ -651,10 +775,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>17.5 ± 28</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>0.0768 ± 0.094</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.00142 ± 0.0028</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.00123 ± 0.00062</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>20.4 ± 7.4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>0.168 ± 0.3</t>
         </is>
@@ -671,14 +815,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -699,10 +847,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>golinski</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>otl_circuit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>piston</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>rastrigin_6d</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -724,12 +892,32 @@
           <t>-2.88 ± 2</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2.33e+03 ± 1.3</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>0.0235 ± 0.082</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2.57 ± 0.0042</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>0.156 ± 0.0038</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>23.1 ± 9.4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>-0.892 ± 0.31</t>
         </is>
@@ -753,10 +941,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2.33e+03 ± 0.93</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>-0.00703 ± 0.067</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2.59 ± 0.0086</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.159 ± 0.0025</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>18.3 ± 3.8</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>-1.01 ± 0.18</t>
         </is>
@@ -780,10 +988,30 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>2.33e+03 ± 1.3</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>-0.0112 ± 0.055</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2.59 ± 0.0053</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.159 ± 0.0035</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>17.1 ± 7.9</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>-1.03 ± 0.16</t>
         </is>
@@ -807,10 +1035,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2.33e+03 ± 2.8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>-0.00875 ± 0.058</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2.6 ± 0.0041</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.162 ± 0.002</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>14.5 ± 2.6</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>-1.02 ± 0.14</t>
         </is>
@@ -834,10 +1082,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2.34e+03 ± 5.5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>0.0155 ± 0.058</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2.6 ± 0.0026</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.164 ± 0.0054</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>17.5 ± 3.4</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>-1.07 ± 0.014</t>
         </is>
@@ -861,10 +1129,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2.36e+03 ± 32</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>0.0236 ± 0.084</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2.57 ± 0.01</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.156 ± 0.0035</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>25.2 ± 7.3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>-0.922 ± 0.28</t>
         </is>
@@ -921,96 +1209,96 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HAEI(γ=0.5)</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="C2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ANPEI(β=0.8)</t>
+          <t>HAEI(γ=0.5)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.92</v>
+        <v>3.38</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D3" s="3" t="n">
         <v>3</v>
       </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>RAHBO(α=0.5)</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ANPEI(β=0.8)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.67</v>
+        <v>3.58</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>RAHBO(α=0.5)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.83</v>
+        <v>3.58</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -1020,16 +1308,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.42</v>
+        <v>3.62</v>
       </c>
       <c r="C7" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1043,14 +1331,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1071,10 +1363,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>golinski</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>otl_circuit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>piston</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>rastrigin_6d</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -1096,12 +1408,32 @@
           <t>0.00181 ± 0.0076</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>37.3 ± 13</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>-6.54e-07 ± 4.2e-07</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.0659 ± 0.03</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.0025 ± 0.0021</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>30.6 ± 9.4</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>1.81e-06 ± 5.8e-06</t>
         </is>
@@ -1125,10 +1457,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>6.39e-05 ± 7.9e-05</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>0.0225 ± 0.048</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.0121 ± 0.014</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.00109 ± 0.0006</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>31.2 ± 2.5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>0.0324 ± 0.12</t>
         </is>
@@ -1150,12 +1502,32 @@
           <t>0.662 ± 0.95</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>0.029 ± 0.049</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>3.07e-05 ± 6.1e-05</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>0.001 ± 0.00074</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>12.2 ± 8</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>0.0457 ± 0.18</t>
         </is>
@@ -1177,12 +1549,32 @@
           <t>0.158 ± 0.39</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>0 ± 0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>0.000174 ± 0.00025</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.0163 ± 0.014</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.00205 ± 0.00054</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>3.89 ± 2.2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.000521 ± 0.00094</t>
         </is>
@@ -1199,14 +1591,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1227,10 +1623,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>golinski</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>otl_circuit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>piston</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>rastrigin_6d</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -1254,10 +1670,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>2.39e+03 ± 13</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>0.0113 ± 0.0036</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2.67 ± 0.03</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.164 ± 0.0025</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>35.6 ± 9.4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>-1.02 ± 0.0037</t>
         </is>
@@ -1281,10 +1717,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2.35e+03 ± 7.9e-05</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>0.0327 ± 0.049</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2.62 ± 0.014</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.162 ± 0.00095</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>36.2 ± 2.5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>-0.986 ± 0.13</t>
         </is>
@@ -1306,12 +1762,32 @@
           <t>-2.98 ± 2</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2.33e+03 ± 1.3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>-0.0112 ± 0.055</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>2.59 ± 0.0053</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>0.159 ± 0.0035</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>17.1 ± 7.9</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>-1.03 ± 0.16</t>
         </is>
@@ -1333,12 +1809,32 @@
           <t>-3.3 ± 1.5</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2.33e+03 ± 0.93</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>-0.0427 ± 0.013</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2.62 ± 0.018</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.163 ± 0.002</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>8.69 ± 2.1</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>-1.07 ± 0.013</t>
         </is>
@@ -1399,13 +1895,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>1.25</v>
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.38</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1416,28 +1912,28 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Heteroscedastic LVGP</t>
+          <t>Categorical kernel</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2.83</v>
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2.08</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAHBO(α=0.5)</t>
+          <t>PI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Categorical kernel</t>
+          <t>Heteroscedastic LVGP</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1447,11 +1943,11 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>2.71</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>RAHBO(α=0.5)</t>
         </is>
       </c>
     </row>
@@ -1462,13 +1958,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.92</v>
+        <v>2.83</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1532,51 +2028,59 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categorical kernel</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Heteroscedastic LVGP</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>RAHBO(α=0.5)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="D4" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="E4" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1587,66 +2091,66 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2</v>
+        <v>8.75</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>HAEI(γ=0.5)</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6.5</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Heteroscedastic LVGP</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="n"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ANPEI(β=0.8)</t>
+          <t>HAEI(γ=0.5)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Heteroscedastic LVGP</t>
+        </is>
+      </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>RAHBO(α=0.5)</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
@@ -1663,11 +2167,11 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>RAHBO(α=0.5)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.25</v>
+        <v>10.12</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -1684,14 +2188,14 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>HAEI(γ=0.5)</t>
+          <t>ANPEI(β=0.8)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10.62</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1700,16 +2204,16 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Categorical kernel</t>
+          <t>Standard LVGP</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ANPEI(β=0.8)</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9.25</v>
+        <v>10.75</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
@@ -1721,57 +2225,61 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Heteroscedastic LVGP</t>
+          <t>Categorical kernel</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>ANPEI(β=0.8)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.5</v>
+        <v>10.88</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Standard LVGP</t>
+        </is>
+      </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9</v>
+        <v>11.25</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Categorical kernel</t>
+          <t>Separate GP</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>HAEI(γ=0.5)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11.75</v>
+        <v>11.38</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1781,56 +2289,48 @@
       <c r="A15" s="2" t="n"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>RAHBO(α=0.5)</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Separate GP</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="n"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ANPEI(β=0.8)</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14.25</v>
+        <v>11.75</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Heteroscedastic LVGP</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="n"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>ANPEI(β=0.8)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.5</v>
+        <v>12.12</v>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1839,19 +2339,19 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Separate GP</t>
+          <t>Heteroscedastic LVGP</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>HAEI(γ=0.5)</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.5</v>
+        <v>13.38</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1861,14 +2361,14 @@
       <c r="A19" s="2" t="n"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>HAEI(γ=0.5)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.75</v>
+        <v>13.38</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1882,57 +2382,59 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.25</v>
+        <v>14.12</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Separate GP</t>
+        </is>
+      </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>RAHBO(α=0.5)</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>19.25</v>
-      </c>
-      <c r="D21" t="n">
-        <v>17</v>
+        <v>14.12</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>RAHBO(α=0.5)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>20.5</v>
+        <v>16.38</v>
       </c>
       <c r="D22" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A14:A15"/>
+  <mergeCells count="4">
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A14:A17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benchmark/notebooks/comparison_tables.xlsx
+++ b/benchmark/notebooks/comparison_tables.xlsx
@@ -461,18 +461,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,40 +484,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>ackley_10d</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>ackley_2d</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>branin_hetero</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>golinski</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>otl_circuit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>piston</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rastrigin_6d</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -528,42 +534,47 @@
           <t>LCB</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>1.39 ± 0.68</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>0.726 ± 1.3</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>0.529 ± 0.88</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>0.0769 ± 0.094</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>0.00142 ± 0.0028</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>0.00104 ± 0.00071</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>18.2 ± 9.6</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>0.2 ± 0.33</t>
         </is>
@@ -577,40 +588,45 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>1.75 ± 0.94</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>0.709 ± 1.3</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>0.238 ± 0.59</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>0.0349 ± 0.062</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>6.94e-05 ± 7e-05</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>0.000532 ± 0.00038</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>13.6 ± 3.8</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>0.0684 ± 0.19</t>
         </is>
@@ -624,40 +640,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>1.75 ± 0.93</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>0.422 ± 1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>0.662 ± 0.95</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>0.029 ± 0.049</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>3.07e-05 ± 6.1e-05</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>0.001 ± 0.00074</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>12.2 ± 8</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>0.0457 ± 0.18</t>
         </is>
@@ -671,40 +692,45 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>2.4 ± 0.41</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>0.425 ± 1</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.434 ± 0.74</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>0.0288 ± 0.049</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>3.07e-05 ± 6.1e-05</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>0.000822 ± 0.00057</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>9.46 ± 2.4</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>0.0486 ± 0.15</t>
         </is>
@@ -716,42 +742,47 @@
           <t>ANPEI(β=0.8)</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3.13 ± 1.2</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>0.116 ± 0.55</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.666 ± 1.1</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>0.0413 ± 0.048</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>0.000162 ± 0.00029</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>0.00209 ± 0.0007</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>12.6 ± 3.4</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>0.000237 ± 0.00041</t>
         </is>
@@ -765,40 +796,45 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>1.72 ± 1.1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>0.723 ± 1.3</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>0.288 ± 0.78</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>17.5 ± 28</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>0.0768 ± 0.094</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>0.00142 ± 0.0028</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>0.00123 ± 0.00062</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>20.4 ± 7.4</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>0.168 ± 0.3</t>
         </is>
@@ -815,18 +851,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -837,40 +874,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>ackley_10d</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>ackley_2d</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>branin_hetero</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>golinski</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>otl_circuit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>piston</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rastrigin_6d</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -882,42 +924,47 @@
           <t>LCB</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>2.58 ± 0.66</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>0.661 ± 1.3</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>-2.88 ± 2</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>2.33e+03 ± 1.3</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>0.0235 ± 0.082</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>2.57 ± 0.0042</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>0.156 ± 0.0038</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>23.1 ± 9.4</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>-0.892 ± 0.31</t>
         </is>
@@ -931,40 +978,45 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>2.95 ± 0.93</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>0.662 ± 1.2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>-2.16 ± 1.9</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2.33e+03 ± 0.93</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>-0.00703 ± 0.067</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2.59 ± 0.0086</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>0.159 ± 0.0025</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>18.3 ± 3.8</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>-1.01 ± 0.18</t>
         </is>
@@ -978,40 +1030,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>2.94 ± 0.9</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>0.375 ± 1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>-2.98 ± 2</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>2.33e+03 ± 1.3</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>-0.0112 ± 0.055</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>2.59 ± 0.0053</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>0.159 ± 0.0035</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>17.1 ± 7.9</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>-1.03 ± 0.16</t>
         </is>
@@ -1025,40 +1082,45 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>3.62 ± 0.37</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>0.368 ± 1</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>-2.7 ± 1.9</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>2.33e+03 ± 2.8</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>-0.00875 ± 0.058</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>2.6 ± 0.0041</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>0.162 ± 0.002</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>14.5 ± 2.6</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>-1.02 ± 0.14</t>
         </is>
@@ -1070,42 +1132,47 @@
           <t>ANPEI(β=0.8)</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4.36 ± 1.3</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>0.0812 ± 0.55</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.359 ± 1.2</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>2.34e+03 ± 5.5</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>0.0155 ± 0.058</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>2.6 ± 0.0026</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>0.164 ± 0.0054</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>17.5 ± 3.4</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>-1.07 ± 0.014</t>
         </is>
@@ -1119,40 +1186,45 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>2.88 ± 1.1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>0.662 ± 1.3</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>-0.135 ± 1.1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>2.36e+03 ± 32</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>0.0236 ± 0.084</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>2.57 ± 0.01</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>0.156 ± 0.0035</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>25.2 ± 7.3</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>-0.922 ± 0.28</t>
         </is>
@@ -1213,16 +1285,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.29</v>
+        <v>3.19</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -1232,7 +1304,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>3</v>
@@ -1241,7 +1313,7 @@
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -1251,7 +1323,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
@@ -1260,64 +1332,64 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ANPEI(β=0.8)</t>
+          <t>RAHBO(α=0.5)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
+        <v>4.5</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RAHBO(α=0.5)</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>3.58</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>ANPEI(β=0.8)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.62</v>
+        <v>3.77</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1331,18 +1403,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1353,40 +1426,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>ackley_10d</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>ackley_2d</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>branin_hetero</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>golinski</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>otl_circuit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>piston</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rastrigin_6d</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -1400,40 +1478,45 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>0.0102 ± 0.0098</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>0.00181 ± 0.0076</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>37.3 ± 13</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>-6.54e-07 ± 4.2e-07</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>0.0659 ± 0.03</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>0.0025 ± 0.0021</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>30.6 ± 9.4</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>1.81e-06 ± 5.8e-06</t>
         </is>
@@ -1447,40 +1530,45 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>0.022 ± 0.031</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>0.0802 ± 0.058</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>6.39e-05 ± 7.9e-05</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>0.0225 ± 0.048</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.0121 ± 0.014</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>0.00109 ± 0.0006</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>31.2 ± 2.5</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>0.0324 ± 0.12</t>
         </is>
@@ -1494,40 +1582,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>1.75 ± 0.93</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>0.422 ± 1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>0.662 ± 0.95</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>0.029 ± 0.049</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>3.07e-05 ± 6.1e-05</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>0.001 ± 0.00074</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>12.2 ± 8</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>0.0457 ± 0.18</t>
         </is>
@@ -1541,40 +1634,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>4.44e-16 ± 0</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
           <t>0.01 ± 0.0092</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.158 ± 0.39</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>0 ± 0</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>0.000174 ± 0.00025</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>0.0163 ± 0.014</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>0.00205 ± 0.00054</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>3.89 ± 2.2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>0.000521 ± 0.00094</t>
         </is>
@@ -1591,18 +1689,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1613,40 +1712,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>ackley_10d</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>ackley_2d</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>branin_hetero</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>golinski</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>griewank_2d</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>otl_circuit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>piston</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rastrigin_6d</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sixhump_camel</t>
         </is>
@@ -1660,40 +1764,45 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>0.0265 ± 0.0095</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>0.372 ± 0.43</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>2.39e+03 ± 13</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>0.0113 ± 0.0036</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>2.67 ± 0.03</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>0.164 ± 0.0025</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>35.6 ± 9.4</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>-1.02 ± 0.0037</t>
         </is>
@@ -1707,40 +1816,45 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>0.0388 ± 0.031</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>0.486 ± 0.47</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2.35e+03 ± 7.9e-05</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>0.0327 ± 0.049</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2.62 ± 0.014</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>0.162 ± 0.00095</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>36.2 ± 2.5</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>-0.986 ± 0.13</t>
         </is>
@@ -1754,40 +1868,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>2.94 ± 0.9</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>0.375 ± 1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>-2.98 ± 2</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>2.33e+03 ± 1.3</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>-0.0112 ± 0.055</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>2.59 ± 0.0053</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>0.159 ± 0.0035</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>17.1 ± 7.9</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>-1.03 ± 0.16</t>
         </is>
@@ -1801,40 +1920,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>1.06 ± 0.025</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
           <t>-0.0355 ± 0.025</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>-3.3 ± 1.5</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>2.33e+03 ± 0.93</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>-0.0427 ± 0.013</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>2.62 ± 0.018</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>0.163 ± 0.002</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>8.69 ± 2.1</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>-1.07 ± 0.013</t>
         </is>
@@ -1916,13 +2040,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1958,17 +2082,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ANPEI(β=0.8)</t>
+          <t>LCB</t>
         </is>
       </c>
     </row>
@@ -2023,43 +2147,43 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Standard LVGP</t>
+          <t>Categorical kernel</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7</v>
+        <v>6.89</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>3</v>
+      <c r="E2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Categorical kernel</t>
+          <t>Standard LVGP</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.62</v>
+        <v>7</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="n">
-        <v>1</v>
+      <c r="E3" s="3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2095,7 +2219,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8.75</v>
+        <v>8.33</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>1</v>
@@ -2112,7 +2236,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.119999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
@@ -2129,31 +2253,27 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9.380000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Heteroscedastic LVGP</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="n"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>RAHBO(α=0.5)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.619999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2162,30 +2282,26 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Categorical kernel</t>
+          <t>Heteroscedastic LVGP</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>RAHBO(α=0.5)</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10.12</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Heteroscedastic LVGP</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="n"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>ANPEI(β=0.8)</t>
@@ -2234,7 +2350,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.88</v>
+        <v>10.78</v>
       </c>
       <c r="D12" t="n">
         <v>3</v>
@@ -2246,7 +2362,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Standard LVGP</t>
+          <t>Separate GP</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -2255,48 +2371,52 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>1</v>
+        <v>11.22</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>Standard LVGP</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>Separate GP</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>HAEI(γ=0.5)</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="C15" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="D15" t="n">
         <v>4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n"/>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -2310,7 +2430,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11.75</v>
+        <v>11.33</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
@@ -2327,7 +2447,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12.12</v>
+        <v>12.11</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
@@ -2337,38 +2457,38 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Heteroscedastic LVGP</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>EI</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="D18" t="n">
-        <v>9</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>HAEI(γ=0.5)</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>13.38</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2378,52 +2498,52 @@
       <c r="A20" s="2" t="n"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>HAEI(γ=0.5)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14.12</v>
+        <v>13.38</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Separate GP</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="n"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>14.12</v>
       </c>
-      <c r="D21" s="3" t="n">
-        <v>1</v>
+      <c r="D21" t="n">
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Separate GP</t>
+        </is>
+      </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>RAHBO(α=0.5)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.38</v>
+        <v>15.33</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -2431,10 +2551,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A5:A8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benchmark/notebooks/comparison_tables.xlsx
+++ b/benchmark/notebooks/comparison_tables.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.47 ± 0.73</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.56 ± 0.73</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1.06 ± 0.025</t>
+          <t>1.07 ± 0.026</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2025,7 +2025,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>3</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2061,13 +2061,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2082,13 +2082,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.11</v>
+        <v>3.33</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.74</v>
+        <v>2.89</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.75</v>
+        <v>7.89</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -2215,34 +2215,34 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>8.33</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>1</v>
+      <c r="D5" t="n">
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
+        <v>8.67</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2263,17 +2263,21 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Heteroscedastic LVGP</t>
+        </is>
+      </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>RAHBO(α=0.5)</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.44</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2282,36 +2286,40 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Heteroscedastic LVGP</t>
+          <t>Categorical kernel</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>RAHBO(α=0.5)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9.619999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Standard LVGP</t>
+        </is>
+      </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ANPEI(β=0.8)</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10.62</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -2320,19 +2328,19 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Standard LVGP</t>
+          <t>Heteroscedastic LVGP</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>ANPEI(β=0.8)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10.75</v>
+        <v>10.62</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -2341,37 +2349,37 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Categorical kernel</t>
+          <t>Standard LVGP</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ANPEI(β=0.8)</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3</v>
+        <v>11.22</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Separate GP</t>
+          <t>Categorical kernel</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ANPEI(β=0.8)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11.22</v>
+        <v>11.33</v>
       </c>
       <c r="D13" t="n">
         <v>3</v>
@@ -2383,7 +2391,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Standard LVGP</t>
+          <t>Separate GP</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -2392,28 +2400,24 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>1</v>
+        <v>11.78</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Separate GP</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="n"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>HAEI(γ=0.5)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11.33</v>
+        <v>11.89</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -2430,7 +2434,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11.33</v>
+        <v>11.89</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
@@ -2447,7 +2451,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12.11</v>
+        <v>12.67</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
@@ -2457,62 +2461,70 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Heteroscedastic LVGP</t>
+        </is>
+      </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13.22</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>13.38</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Heteroscedastic LVGP</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>HAEI(γ=0.5)</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>13.38</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Separate GP</t>
+        </is>
+      </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>HAEI(γ=0.5)</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="D20" t="n">
-        <v>6</v>
+        <v>13.67</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Heteroscedastic LVGP</t>
+        </is>
+      </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>PI</t>
@@ -2540,21 +2552,20 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.33</v>
+        <v>15.89</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="A5:A8"/>
+  <mergeCells count="3">
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A14:A17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
